--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2454,7 +2454,7 @@
         <v>46277</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>46277.42944444445</v>
+        <v>46278.47146990741</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2454,7 +2454,7 @@
         <v>46277</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>46278.47146990741</v>
+        <v>46279.50689814815</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2457,6 +2457,35 @@
         <v>46279.50689814815</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>46280.00064159722</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>46280.47255787037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2486,6 +2486,35 @@
         <v>46280.47255787037</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>46281.0008534375</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>46281</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>46281.46103009259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2515,6 +2515,35 @@
         <v>46281.46103009259</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>46282.00104342592</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>46282</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>46282.46803240741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2544,6 +2544,35 @@
         <v>46282.46803240741</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>46283.00059936343</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>46283.4491550926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2573,6 +2573,35 @@
         <v>46283.4491550926</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>46284.00075885417</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>46284</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>46284.43818287037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2599,7 +2599,7 @@
         <v>46284</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>46284.43818287037</v>
+        <v>46285.45368055555</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2599,7 +2599,7 @@
         <v>46284</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>46285.45368055555</v>
+        <v>46286.51280092593</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2602,6 +2602,35 @@
         <v>46286.51280092593</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>46287.00085028935</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>46287.46565972222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2631,6 +2631,35 @@
         <v>46287.46565972222</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>46288.00083880787</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>46288</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>46288.45934027778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2660,6 +2660,35 @@
         <v>46288.45934027778</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>46289.00083677084</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>46289.47226851852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2689,6 +2689,35 @@
         <v>46289.47226851852</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>46290.004170625</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>46290.47582175926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2718,6 +2718,35 @@
         <v>46290.47582175926</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>46291.00076711806</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>46291</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>46291.45869212963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2744,7 +2744,7 @@
         <v>46291</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>46291.45869212963</v>
+        <v>46292.48578703704</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2744,7 +2744,7 @@
         <v>46291</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>46292.48578703704</v>
+        <v>46293.5519212963</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2747,6 +2747,35 @@
         <v>46293.5519212963</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>46294.00072908564</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>46294.5156712963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2776,6 +2776,35 @@
         <v>46294.5156712963</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>46295.00074290509</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>46295.50537037037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2805,6 +2805,35 @@
         <v>46295.50537037037</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>46296.00069483796</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>46296.52861111111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2834,6 +2834,35 @@
         <v>46296.52861111111</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>46297.00087646991</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>46297.50400462963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2863,6 +2863,35 @@
         <v>46297.50400462963</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>46298.01131697917</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>46298</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>46298.47034722222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2889,7 +2889,7 @@
         <v>46298</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>46298.47034722222</v>
+        <v>46299.49790509259</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2889,7 +2889,7 @@
         <v>46298</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>46299.49790509259</v>
+        <v>46300.58170138889</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2892,6 +2892,35 @@
         <v>46300.58170138889</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>46301.00426755787</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>46301.54171296296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2921,6 +2921,35 @@
         <v>46301.54171296296</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>46302.00095275463</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>46302.53682870371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2950,6 +2950,35 @@
         <v>46302.53682870371</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>46303.00077490741</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>46303</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>46303.54273148148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2979,6 +2979,35 @@
         <v>46303.54273148148</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>46304.0007838426</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>46304.53342592593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3008,6 +3008,35 @@
         <v>46304.53342592593</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>46305.00423440972</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>46305.50424768519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -3034,7 +3034,7 @@
         <v>46305</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>46305.50424768519</v>
+        <v>46306.51381944444</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -3034,7 +3034,7 @@
         <v>46305</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>46306.51381944444</v>
+        <v>46307.61549768518</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3037,6 +3037,35 @@
         <v>46307.61549768518</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>46308.00081677084</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>46308.5749537037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3066,6 +3066,35 @@
         <v>46308.5749537037</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>46309.00412949074</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>46309.47591435185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3095,6 +3095,35 @@
         <v>46309.47591435185</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>46310.00432640046</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>46310.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3124,6 +3124,35 @@
         <v>46310.46</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>46311.00108375</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>46311.45685185185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3153,6 +3153,35 @@
         <v>46311.45685185185</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>46312.00084172453</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>46312</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>46312.43018518519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -3179,7 +3179,7 @@
         <v>46312</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>46312.43018518519</v>
+        <v>46313.44107638889</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -3179,7 +3179,7 @@
         <v>46312</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>46313.44107638889</v>
+        <v>46314.52182870371</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3182,6 +3182,35 @@
         <v>46314.52182870371</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>46315.00408082176</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>46315.46288194445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3211,6 +3211,35 @@
         <v>46315.46288194445</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>46316.00076111111</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>46316.47415509259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3240,6 +3240,35 @@
         <v>46316.47415509259</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>46317.00076641203</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>46317.47401620371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3269,6 +3269,35 @@
         <v>46317.47401620371</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>46318.00078961805</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>46318.46719907408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3298,6 +3298,35 @@
         <v>46318.46719907408</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>46319.000619375</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>46319</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>46319.43840277778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -3324,7 +3324,7 @@
         <v>46319</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>46319.43840277778</v>
+        <v>46320.45655092593</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -3324,7 +3324,7 @@
         <v>46319</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>46320.45655092593</v>
+        <v>46321.51996527778</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3327,6 +3327,35 @@
         <v>46321.51996527778</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>46322.0009671875</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>46322.49096064815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3356,6 +3356,35 @@
         <v>46322.49096064815</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>46323.00446289352</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>46323.51466435185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3385,6 +3385,35 @@
         <v>46323.51466435185</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>46324.00088011574</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>46324.52086805556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3414,6 +3414,35 @@
         <v>46324.52086805556</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>46325.00075084491</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>46325.51519675926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3443,6 +3443,35 @@
         <v>46325.51519675926</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>46326.02493356481</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>46326</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>46326.49487268519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
